--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_349_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_349_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M3" t="n">
         <v>14</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>1</v>
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2119,10 +2119,10 @@
         <v>18</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2315,7 +2315,7 @@
         <v>14</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2517,10 +2517,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X23" t="n">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>2</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3099,16 +3099,16 @@
         <v>12</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X26" t="n">
         <v>4</v>
@@ -3827,16 +3827,16 @@
         <v>76</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X30" t="n">
         <v>20</v>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V36" t="n">
         <v>0</v>
@@ -5082,10 +5082,10 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="X39" t="n">
         <v>11</v>
@@ -5664,10 +5664,10 @@
         <v>5</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6056,10 +6056,10 @@
         <v>23</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6258,10 +6258,10 @@
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>5</v>
@@ -6784,16 +6784,16 @@
         <v>118</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X48" t="n">
         <v>40</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_349_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_349_EL.xlsx
@@ -674,10 +674,10 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="O2" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -695,17 +695,17 @@
         <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="V2" t="n">
         <v>8</v>
       </c>
       <c r="W2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>62.50</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>14</v>
       </c>
       <c r="N3" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="O3" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>80.00</t>
+          <t>61.54</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1579,18 +1579,18 @@
         <v>1</v>
       </c>
       <c r="AH18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
@@ -1739,14 +1739,14 @@
         <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2131,10 +2131,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
@@ -2178,11 +2178,11 @@
         <v>1</v>
       </c>
       <c r="AK21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
@@ -3839,14 +3839,14 @@
         <v>4</v>
       </c>
       <c r="X30" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="Y30" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,22 +3875,22 @@
         <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
         <v>8</v>
       </c>
       <c r="AK30" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -5088,14 +5088,14 @@
         <v>4</v>
       </c>
       <c r="X39" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Y39" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>68.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,10 +5676,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Y44" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
         <v>6</v>
       </c>
       <c r="X48" t="n">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="Y48" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="AA48" t="n">
